--- a/resultados/comparacao_artigos.xlsx
+++ b/resultados/comparacao_artigos.xlsx
@@ -439,11 +439,15 @@
           <t>Renda</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>0.732123640088135</v>
+      </c>
       <c r="C2" t="n">
         <v>13.4058092545133</v>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>2.444839257690192</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -455,7 +459,9 @@
       <c r="C3" t="n">
         <v>5.487158702099044</v>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>2.772719178847556</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -467,7 +473,9 @@
       <c r="C4" t="n">
         <v>-1.298657375174292</v>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>2.432962513979838</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -475,7 +483,9 @@
           <t>Política</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>5.031839759259635</v>
+      </c>
       <c r="C5" t="n">
         <v>3.757615129001593</v>
       </c>
